--- a/artfynd/A 18338-2025 artfynd.xlsx
+++ b/artfynd/A 18338-2025 artfynd.xlsx
@@ -675,56 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118288834</v>
+        <v>118356269</v>
       </c>
       <c r="B2" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6020</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>långtjärnen, Jmt</t>
+          <t>Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505228</v>
+        <v>505290</v>
       </c>
       <c r="R2" t="n">
-        <v>7004067</v>
+        <v>7003898</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118356275</v>
+        <v>118356271</v>
       </c>
       <c r="B3" t="n">
-        <v>79080</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505022</v>
+        <v>505221</v>
       </c>
       <c r="R3" t="n">
-        <v>7003838</v>
+        <v>7004088</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,37 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118356268</v>
+        <v>118356272</v>
       </c>
       <c r="B4" t="n">
-        <v>78227</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505288</v>
+        <v>505144</v>
       </c>
       <c r="R4" t="n">
-        <v>7003895</v>
+        <v>7004057</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,57 +1008,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118356272</v>
+        <v>118288834</v>
       </c>
       <c r="B5" t="n">
-        <v>90920</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>6020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Jmt</t>
+          <t>långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505144</v>
+        <v>505228</v>
       </c>
       <c r="R5" t="n">
-        <v>7004057</v>
+        <v>7004067</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,37 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118356271</v>
+        <v>118356268</v>
       </c>
       <c r="B6" t="n">
-        <v>90920</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1173,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505221</v>
+        <v>505288</v>
       </c>
       <c r="R6" t="n">
-        <v>7004088</v>
+        <v>7003895</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,12 +1223,7 @@
         <v>118356270</v>
       </c>
       <c r="B7" t="n">
-        <v>78227</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118356269</v>
+        <v>118356273</v>
       </c>
       <c r="B8" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505290</v>
+        <v>505129</v>
       </c>
       <c r="R8" t="n">
-        <v>7003898</v>
+        <v>7004090</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,37 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118356273</v>
+        <v>118356275</v>
       </c>
       <c r="B9" t="n">
-        <v>97770</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1521,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505129</v>
+        <v>505022</v>
       </c>
       <c r="R9" t="n">
-        <v>7004090</v>
+        <v>7003838</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1556,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18338-2025 artfynd.xlsx
+++ b/artfynd/A 18338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356269</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118288834</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356268</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356273</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,8 +1590,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>